--- a/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-007_帳票設計書.xlsx
+++ b/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-007_帳票設計書.xlsx
@@ -76,7 +76,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -98,11 +98,50 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,6 +162,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -500,6 +543,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -508,6 +554,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -519,7 +567,7 @@
           <t>勤怠フロー</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -532,7 +580,7 @@
           <t>KF-BD-007</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -542,10 +590,10 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -558,7 +606,7 @@
           <t>2026/10/03</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -571,8 +619,10 @@
           <t>Wang Sheng</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
+      <c r="D12" s="10" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -619,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -678,6 +728,29 @@
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>実装（ReportService / AdminReportController / ReportRepository）と照合。RPT-001 のファイル名（yyyyMM）・CSV 仕様（BOM・CRLF・エスケープ・並び順・対象者・休暇日数の月帰属）を実装に合わせて修正。RPT-002 は未実装と明記</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -691,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -700,50 +773,56 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>※Excelで直接開けるようBOM付きとする。PDF帳票は将来拡張。</t>
+          <t>※Excelで直接開けるようBOM付きとする。PDF帳票は将来拡張。実装済みは RPT-001 のみ（API-018 format=csv）。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>帳票ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>帳票名</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>出力画面</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>出力権限</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>文字コード</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>ファイル名</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>実装状況・備考</t>
         </is>
       </c>
     </row>
@@ -780,7 +859,12 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>kintai_summary_yyyymm.csv</t>
+          <t>kintai_summary_yyyyMM.csv</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>実装済。GET /api/admin/reports/monthly?month=yyyy-MM[&amp;departmentId=]&amp;format=csv。改行 CRLF。Content-Disposition: attachment、Cache-Control: no-store</t>
         </is>
       </c>
     </row>
@@ -818,6 +902,11 @@
       <c r="G5" s="8" t="inlineStr">
         <is>
           <t>leave_status_yyyymm.csv</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>未実装（今後）。出力する API・画面操作は存在しない</t>
         </is>
       </c>
     </row>
@@ -833,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -846,7 +935,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>1行目はヘッダー行。対象月・部署で絞り込み。ユーザー・部署順に出力。</t>
+          <t>1行目はヘッダー行（社員ID,氏名,部署,出勤日数,総勤務時間,残業時間,休暇取得日数）。対象月・部署で絞り込み。部署（部署なしは最後）・社員ID の順に出力。区切りはカンマ、改行は CRLF。</t>
         </is>
       </c>
     </row>
@@ -878,8 +967,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>1</v>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -899,8 +990,10 @@
       <c r="E4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>2</v>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -917,11 +1010,17 @@
           <t>文字列</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>先頭が = + - @ タブ CR の場合は先頭に ' を付与（数式インジェクション対策）。カンマ・二重引用符・改行を含む場合は二重引用符で囲む</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>3</v>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -938,11 +1037,17 @@
           <t>文字列</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>部署なしは空欄（同様のエスケープ）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>4</v>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
@@ -961,13 +1066,15 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>勤務日の件数</t>
+          <t>対象月の出勤打刻（clock_in あり）の件数</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>5</v>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -986,13 +1093,15 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>合計</t>
+          <t>合計。分を H:mm に換算（例：6930 分 → 115:30）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>6</v>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
@@ -1011,13 +1120,15 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>合計</t>
+          <t>合計。換算は同上</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>7</v>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1147,14 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>承認済みの休暇申請</t>
+          <t>承認済み（APPROVED）の休暇申請のうち開始日が対象月のもの。月をまたぐ休暇は開始日の月に全日数を計上</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>対象者：入社日が対象月末以前で、在籍（ACTIVE）、または対象月に打刻・承認済み休暇の実績がある社員（退職者でも実績があれば出力）。同じ集計を JSON（format=json）で画面表示に使う。</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1223,6 +1341,13 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>※RPT-002 は未実装（今後）。上記は設計案。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
